--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487621_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487621_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9486</v>
+        <v>7.3123</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4596</v>
+        <v>4.6598</v>
       </c>
       <c r="F2" t="n">
-        <v>2.489</v>
+        <v>2.6525</v>
       </c>
       <c r="G2" t="n">
         <v>7.4928</v>
@@ -610,13 +610,13 @@
         <v>2.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0069</v>
+        <v>-0.6432</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7874</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2196</v>
+        <v>-0.0561</v>
       </c>
       <c r="V2" t="n">
         <v>-2.4477</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7931</v>
+        <v>4.7324</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1405</v>
+        <v>2.1615</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6527</v>
+        <v>2.5709</v>
       </c>
       <c r="G3" t="n">
         <v>6.4922</v>
@@ -688,13 +688,13 @@
         <v>3.8806</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7095</v>
+        <v>-0.7702</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3623</v>
+        <v>-0.3413</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3472</v>
+        <v>-0.429</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9896</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2335</v>
+        <v>4.576</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4173</v>
+        <v>1.678</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8162</v>
+        <v>2.898</v>
       </c>
       <c r="G4" t="n">
         <v>4.1032</v>
@@ -766,13 +766,13 @@
         <v>2.5224</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.734</v>
+        <v>-0.3914</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7627</v>
+        <v>-0.5019</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0287</v>
+        <v>0.1105</v>
       </c>
       <c r="V4" t="n">
         <v>0.2821</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>D. VAZQUEZ JEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5431</v>
+        <v>3.0803</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2354</v>
+        <v>-0.8678</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3077</v>
+        <v>3.9481</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5476</v>
+        <v>0.4287</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6963</v>
+        <v>-0.4828</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8513</v>
+        <v>0.9114</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6089</v>
+        <v>-0.3148</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4871</v>
+        <v>-0.4366</v>
       </c>
       <c r="L5" t="n">
         <v>0.1218</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9387</v>
+        <v>0.7435</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2092</v>
+        <v>-0.0462</v>
       </c>
       <c r="O5" t="n">
-        <v>1.7295</v>
+        <v>0.7897</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3582</v>
+        <v>2.3284</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5224</v>
+        <v>3.2985</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1389</v>
+        <v>-0.6185</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7907</v>
+        <v>-0.429</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9295</v>
+        <v>-0.1895</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2239</v>
+        <v>0.9418</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8462</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2239</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. VAZQUEZ JEREZ</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0564</v>
+        <v>2.9025</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7282</v>
+        <v>0.2949</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7845</v>
+        <v>2.6075</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4287</v>
+        <v>3.5476</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4828</v>
+        <v>1.6963</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9114</v>
+        <v>1.8513</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3148</v>
+        <v>1.6089</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4366</v>
+        <v>1.4871</v>
       </c>
       <c r="L6" t="n">
         <v>0.1218</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7435</v>
+        <v>1.9387</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0462</v>
+        <v>0.2092</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7897</v>
+        <v>1.7295</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3284</v>
+        <v>1.3582</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2985</v>
+        <v>2.5224</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6424</v>
+        <v>-0.7795</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2894</v>
+        <v>-0.1498</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.353</v>
+        <v>-0.6297</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9418</v>
+        <v>-1.2239</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8462</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0955</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MARTIN GONZALEZ</t>
+          <t>A. SANTANA OJEDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5335</v>
+        <v>2.0311</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7433</v>
+        <v>1.4248</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2768</v>
+        <v>0.6063</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0408</v>
+        <v>1.5278</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3073</v>
+        <v>2.8802</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3481</v>
+        <v>-1.3524</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0282</v>
+        <v>1.9416</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2431</v>
+        <v>3.4108</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2712</v>
+        <v>-1.4692</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9874000000000001</v>
+        <v>-0.4138</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.5306</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9231</v>
+        <v>0.1168</v>
       </c>
       <c r="P7" t="n">
+        <v>1.5523</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.194</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-2.9105</v>
-      </c>
       <c r="R7" t="n">
-        <v>2.7164</v>
+        <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1564</v>
+        <v>-0.7669</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6405</v>
+        <v>-0.3228</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7968</v>
+        <v>-0.4441</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6119</v>
+        <v>-0.2821</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SANTANA OJEDA</t>
+          <t>A. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1369</v>
+        <v>0.54</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8032</v>
+        <v>-2.7828</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3337</v>
+        <v>3.3228</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5278</v>
+        <v>-0.0408</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8802</v>
+        <v>0.3073</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3524</v>
+        <v>-0.3481</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9416</v>
+        <v>-1.0282</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4108</v>
+        <v>0.2431</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4692</v>
+        <v>-1.2712</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4138</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5306</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1168</v>
+        <v>0.9231</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5523</v>
+        <v>-0.194</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.194</v>
+        <v>-2.9105</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7463</v>
+        <v>2.7164</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6611</v>
+        <v>0.1629</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9444</v>
+        <v>-0.68</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7167</v>
+        <v>0.8429</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2821</v>
+        <v>0.6119</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8358</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3893</v>
+        <v>-0.1102</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6353</v>
+        <v>-0.2744</v>
       </c>
       <c r="F9" t="n">
-        <v>0.246</v>
+        <v>0.1642</v>
       </c>
       <c r="G9" t="n">
         <v>0.0931</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0063</v>
+        <v>0.2728</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.157</v>
+        <v>0.2038</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1508</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2821</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0061</v>
+        <v>-1.6969</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3971</v>
+        <v>-2.1969</v>
       </c>
       <c r="F10" t="n">
-        <v>0.391</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5719</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.57</v>
+        <v>-0.2608</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2423</v>
+        <v>-0.0421</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3277</v>
+        <v>-0.2187</v>
       </c>
       <c r="V10" t="n">
         <v>0.3299</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9494</v>
+        <v>-2.8616</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0406</v>
+        <v>-2.9801</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0912</v>
+        <v>0.1185</v>
       </c>
       <c r="G11" t="n">
         <v>1.0761</v>
@@ -1312,13 +1312,13 @@
         <v>3.6866</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9643</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.5317</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3721</v>
+        <v>-0.3448</v>
       </c>
       <c r="V11" t="n">
         <v>-4.6134</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>19.9003</v>
+        <v>20.5059</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5115000000000012</v>
+        <v>1.117000000000001</v>
       </c>
       <c r="F12" t="n">
         <v>19.3888</v>
@@ -1390,16 +1390,16 @@
         <v>23.2837</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.276999999999999</v>
+        <v>-4.6713</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.9875</v>
+        <v>-3.382</v>
       </c>
       <c r="U12" t="n">
         <v>-1.2895</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.673100000000001</v>
+        <v>-7.673100000000002</v>
       </c>
       <c r="W12" t="n">
         <v>4.0924</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3501</v>
+        <v>2.641</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7013</v>
+        <v>-0.1788</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3511</v>
+        <v>2.8197</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.9064</v>
+        <v>-2.6524</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3314</v>
+        <v>-2.4906</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.575</v>
+        <v>-0.1619</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8858</v>
+        <v>-1.7772</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3728</v>
+        <v>-1.899</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.487</v>
+        <v>0.1218</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.7922</v>
+        <v>-0.8752</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.7042</v>
+        <v>-0.5916</v>
       </c>
       <c r="O13" t="n">
-        <v>0.912</v>
+        <v>-0.2836</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5821</v>
+        <v>1.7463</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3284</v>
+        <v>1.7463</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4969</v>
+        <v>1.0038</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1603</v>
+        <v>0.0925</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3365</v>
+        <v>0.9113</v>
       </c>
       <c r="V13" t="n">
-        <v>3.3418</v>
+        <v>2.5433</v>
       </c>
       <c r="W13" t="n">
-        <v>4.5656</v>
+        <v>1.506</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2239</v>
+        <v>1.0373</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9586</v>
+        <v>2.1537</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7794</v>
+        <v>2.7013</v>
       </c>
       <c r="F14" t="n">
-        <v>2.738</v>
+        <v>-0.5475</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.6524</v>
+        <v>-1.9064</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.4906</v>
+        <v>-1.3314</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1619</v>
+        <v>-0.575</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.7772</v>
+        <v>0.8858</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.899</v>
+        <v>2.3728</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1218</v>
+        <v>-1.487</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8752</v>
+        <v>-2.7922</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5916</v>
+        <v>-3.7042</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2836</v>
+        <v>0.912</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7463</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7463</v>
+        <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3214</v>
+        <v>1.3005</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5081</v>
+        <v>0.1603</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8295</v>
+        <v>1.1401</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5433</v>
+        <v>3.3418</v>
       </c>
       <c r="W14" t="n">
-        <v>1.506</v>
+        <v>4.5656</v>
       </c>
       <c r="X14" t="n">
-        <v>1.0373</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-1.2168</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4107</v>
+        <v>-0.29</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0029</v>
+        <v>-0.9268</v>
       </c>
       <c r="G15" t="n">
         <v>-2.7575</v>
@@ -1624,13 +1624,13 @@
         <v>0.9702</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1951</v>
+        <v>0.5706</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5843</v>
+        <v>-0.1164</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6108</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. PETIT</t>
+          <t>D. CARABALLO ROPERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1571</v>
+        <v>-1.2908</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0742</v>
+        <v>-1.3595</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0829</v>
+        <v>0.0687</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.573</v>
+        <v>-1.1907</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6898</v>
+        <v>-0.5067</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1168</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5643</v>
+        <v>-0.6055</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5643</v>
+        <v>0.0618</v>
       </c>
       <c r="L16" t="n">
+        <v>-0.6673</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.5852000000000001</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.5685</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.194</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.7761</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.0939</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.2162</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.1222</v>
+      </c>
+      <c r="V16" t="n">
         <v>0</v>
       </c>
-      <c r="M16" t="n">
-        <v>-1.0087</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-1.1254</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.1168</v>
-      </c>
-      <c r="P16" t="n">
-        <v>-1.7463</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-2.9105</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.1642</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.2786</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-0.0471</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.3257</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.8836</v>
-      </c>
       <c r="W16" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. CARABALLO ROPERO</t>
+          <t>D. PETIT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2997</v>
+        <v>-1.3418</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2594</v>
+        <v>-1.1743</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0403</v>
+        <v>-0.1675</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1907</v>
+        <v>-1.573</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5067</v>
+        <v>-1.6898</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.1168</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6055</v>
+        <v>-0.5643</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0618</v>
+        <v>-0.5643</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6673</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-1.0087</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5685</v>
+        <v>-1.1254</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0167</v>
+        <v>0.1168</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.194</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S17" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0939</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3163</v>
+        <v>-0.1472</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2313</v>
+        <v>0.2412</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.8836</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.5031</v>
+        <v>-3.3273</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8718</v>
+        <v>-3.072</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6313</v>
+        <v>-0.2553</v>
       </c>
       <c r="G18" t="n">
         <v>-3.9267</v>
@@ -1858,13 +1858,13 @@
         <v>1.7463</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7893</v>
+        <v>0.9651</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5484</v>
+        <v>0.3482</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2409</v>
+        <v>0.6169</v>
       </c>
       <c r="V18" t="n">
         <v>0.7985</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.1235</v>
+        <v>-3.9661</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.377</v>
+        <v>-3.6773</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.2888</v>
       </c>
       <c r="G19" t="n">
         <v>-1.451</v>
@@ -1936,13 +1936,13 @@
         <v>1.7463</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6857</v>
+        <v>0.8431</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6325</v>
+        <v>0.3322</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0532</v>
+        <v>0.5109</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2239</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.3143</v>
+        <v>-4.1959</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.2426</v>
+        <v>-5.642</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9283</v>
+        <v>1.4461</v>
       </c>
       <c r="G20" t="n">
         <v>-3.8622</v>
@@ -2014,13 +2014,13 @@
         <v>1.5523</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.782</v>
+        <v>0.3365</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4475</v>
+        <v>0.1531</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3344</v>
+        <v>0.1834</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2821</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.218999999999999</v>
+        <v>-8.021599999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.8964</v>
+        <v>-6.6962</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3226</v>
+        <v>-1.3254</v>
       </c>
       <c r="G21" t="n">
         <v>-3.8287</v>
@@ -2092,13 +2092,13 @@
         <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2068</v>
+        <v>1.4042</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0504</v>
+        <v>0.2506</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1564</v>
+        <v>1.1536</v>
       </c>
       <c r="V21" t="n">
         <v>0.6119</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-19.9002</v>
+        <v>-18.5656</v>
       </c>
       <c r="E22" t="n">
         <v>-19.3888</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5113000000000001</v>
+        <v>0.8232000000000002</v>
       </c>
       <c r="G22" t="n">
         <v>-23.1486</v>
@@ -2170,13 +2170,13 @@
         <v>13.5824</v>
       </c>
       <c r="S22" t="n">
-        <v>5.2768</v>
+        <v>6.611599999999999</v>
       </c>
       <c r="T22" t="n">
         <v>1.2895</v>
       </c>
       <c r="U22" t="n">
-        <v>3.9873</v>
+        <v>5.3222</v>
       </c>
       <c r="V22" t="n">
         <v>7.6731</v>
